--- a/htr-FHIR/ig/StructureDefinition-fr-core-associated-entity.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-associated-entity.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="795" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="795" uniqueCount="153">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T12:52:51+00:00</t>
+    <t>2025-02-24T13:32:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -311,10 +311,6 @@
   </si>
   <si>
     <t>InfrastructureRoot.typeId</t>
-  </si>
-  <si>
-    <t xml:space="preserve">II-1:An II instance must have either a root or an nullFlavor. {root.exists() or nullFlavor.exists()}
-</t>
   </si>
   <si>
     <t>AssociatedEntity.typeId.nullFlavor</t>
@@ -1348,7 +1344,7 @@
         <v>74</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>74</v>
@@ -1356,10 +1352,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1457,39 +1453,39 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E7" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="F7" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G7" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H7" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I7" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J7" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K7" t="s" s="2">
         <v>101</v>
-      </c>
-      <c r="F7" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G7" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H7" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I7" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J7" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K7" t="s" s="2">
-        <v>102</v>
       </c>
       <c r="L7" s="2"/>
       <c r="M7" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1540,7 +1536,7 @@
         <v>74</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>80</v>
@@ -1560,39 +1556,39 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E8" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="F8" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G8" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H8" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I8" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J8" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K8" t="s" s="2">
         <v>106</v>
-      </c>
-      <c r="F8" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G8" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H8" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I8" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J8" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K8" t="s" s="2">
-        <v>107</v>
       </c>
       <c r="L8" s="2"/>
       <c r="M8" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1643,7 +1639,7 @@
         <v>74</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>80</v>
@@ -1663,39 +1659,39 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E9" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="F9" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G9" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K9" t="s" s="2">
         <v>111</v>
-      </c>
-      <c r="F9" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G9" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K9" t="s" s="2">
-        <v>112</v>
       </c>
       <c r="L9" s="2"/>
       <c r="M9" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1704,49 +1700,49 @@
       </c>
       <c r="Q9" s="2"/>
       <c r="R9" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="S9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF9" t="s" s="2">
         <v>114</v>
-      </c>
-      <c r="S9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF9" t="s" s="2">
-        <v>115</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>80</v>
@@ -1766,17 +1762,17 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E10" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F10" t="s" s="2">
         <v>75</v>
@@ -1794,11 +1790,11 @@
         <v>74</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L10" s="2"/>
       <c r="M10" t="s" s="2">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1849,7 +1845,7 @@
         <v>74</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>80</v>
@@ -1869,10 +1865,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1899,7 +1895,7 @@
       </c>
       <c r="L11" s="2"/>
       <c r="M11" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -1950,7 +1946,7 @@
         <v>74</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>80</v>
@@ -1970,10 +1966,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -1999,7 +1995,7 @@
         <v>85</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M12" s="2"/>
       <c r="N12" s="2"/>
@@ -2031,7 +2027,7 @@
       </c>
       <c r="Y12" s="2"/>
       <c r="Z12" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>74</v>
@@ -2049,7 +2045,7 @@
         <v>74</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>75</v>
@@ -2069,10 +2065,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2098,7 +2094,7 @@
         <v>95</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="M13" s="2"/>
       <c r="N13" s="2"/>
@@ -2150,7 +2146,7 @@
         <v>74</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -2170,10 +2166,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2271,39 +2267,39 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E15" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="F15" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G15" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H15" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I15" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J15" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K15" t="s" s="2">
         <v>101</v>
-      </c>
-      <c r="F15" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G15" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H15" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I15" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J15" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K15" t="s" s="2">
-        <v>102</v>
       </c>
       <c r="L15" s="2"/>
       <c r="M15" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2354,7 +2350,7 @@
         <v>74</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -2374,39 +2370,39 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E16" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="F16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G16" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K16" t="s" s="2">
         <v>106</v>
-      </c>
-      <c r="F16" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G16" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H16" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I16" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J16" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K16" t="s" s="2">
-        <v>107</v>
       </c>
       <c r="L16" s="2"/>
       <c r="M16" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2457,7 +2453,7 @@
         <v>74</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -2477,41 +2473,41 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E17" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="F17" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G17" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K17" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="F17" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G17" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H17" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I17" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J17" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K17" t="s" s="2">
-        <v>112</v>
-      </c>
       <c r="L17" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>132</v>
-      </c>
-      <c r="M17" t="s" s="2">
-        <v>133</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2562,7 +2558,7 @@
         <v>74</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -2582,41 +2578,41 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E18" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="F18" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G18" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K18" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L18" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="M18" t="s" s="2">
         <v>117</v>
-      </c>
-      <c r="F18" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G18" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H18" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I18" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J18" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K18" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="L18" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>118</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2667,7 +2663,7 @@
         <v>74</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -2687,10 +2683,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2713,7 +2709,7 @@
         <v>74</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="L19" s="2"/>
       <c r="M19" s="2"/>
@@ -2766,7 +2762,7 @@
         <v>74</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -2786,10 +2782,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2812,10 +2808,10 @@
         <v>74</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>139</v>
-      </c>
-      <c r="L20" t="s" s="2">
-        <v>140</v>
       </c>
       <c r="M20" s="2"/>
       <c r="N20" s="2"/>
@@ -2847,7 +2843,7 @@
       </c>
       <c r="Y20" s="2"/>
       <c r="Z20" t="s" s="2">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>74</v>
@@ -2865,7 +2861,7 @@
         <v>74</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -2885,10 +2881,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -2911,10 +2907,10 @@
         <v>74</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="L21" t="s" s="2">
         <v>143</v>
-      </c>
-      <c r="L21" t="s" s="2">
-        <v>144</v>
       </c>
       <c r="M21" s="2"/>
       <c r="N21" s="2"/>
@@ -2966,7 +2962,7 @@
         <v>74</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -2986,10 +2982,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3012,10 +3008,10 @@
         <v>74</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="L22" t="s" s="2">
         <v>146</v>
-      </c>
-      <c r="L22" t="s" s="2">
-        <v>147</v>
       </c>
       <c r="M22" s="2"/>
       <c r="N22" s="2"/>
@@ -3067,7 +3063,7 @@
         <v>74</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -3087,10 +3083,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3113,10 +3109,10 @@
         <v>74</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>149</v>
-      </c>
-      <c r="L23" t="s" s="2">
-        <v>150</v>
       </c>
       <c r="M23" s="2"/>
       <c r="N23" s="2"/>
@@ -3168,7 +3164,7 @@
         <v>74</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -3188,10 +3184,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3214,10 +3210,10 @@
         <v>74</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="L24" t="s" s="2">
         <v>152</v>
-      </c>
-      <c r="L24" t="s" s="2">
-        <v>153</v>
       </c>
       <c r="M24" s="2"/>
       <c r="N24" s="2"/>
@@ -3269,7 +3265,7 @@
         <v>74</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-associated-entity.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-associated-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T13:32:36+00:00</t>
+    <t>2025-02-24T13:36:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-associated-entity.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-associated-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T13:36:50+00:00</t>
+    <t>2025-03-04T16:07:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-associated-entity.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-associated-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-04T16:07:16+00:00</t>
+    <t>2025-03-06T10:23:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-associated-entity.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-associated-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T10:23:19+00:00</t>
+    <t>2025-03-10T13:00:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-associated-entity.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-associated-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-10T13:00:25+00:00</t>
+    <t>2025-03-11T15:29:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-associated-entity.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-associated-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T15:29:00+00:00</t>
+    <t>2025-03-12T13:18:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-associated-entity.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-associated-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-12T13:18:22+00:00</t>
+    <t>2025-03-14T15:47:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-associated-entity.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-associated-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-14T15:47:10+00:00</t>
+    <t>2025-03-25T13:52:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-associated-entity.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-associated-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-25T13:52:25+00:00</t>
+    <t>2025-03-25T14:07:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-associated-entity.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-associated-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-25T14:07:20+00:00</t>
+    <t>2025-03-31T09:17:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-associated-entity.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-associated-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T09:17:15+00:00</t>
+    <t>2025-04-14T15:21:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-associated-entity.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-associated-entity.xlsx
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>associatedEntity</t>
+    <t>CDA - associatedEntity</t>
   </si>
   <si>
     <t>Status</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-14T15:21:44+00:00</t>
+    <t>2025-04-23T09:31:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -793,42 +793,42 @@
   <dimension ref="A1:AK24"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="45.8984375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="45.8984375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="8.95703125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="24.9375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="39.34765625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="39.34765625" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="7.6796875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="21.37890625" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="151.96875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="130.28515625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="15.6640625" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="13.4296875" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="21.57421875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="97.74609375" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="35.75390625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="18.49609375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="83.80078125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="30.65234375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="24.98046875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="21.4140625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/htr-FHIR/ig/StructureDefinition-fr-core-associated-entity.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-associated-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-23T09:31:53+00:00</t>
+    <t>2025-04-24T14:52:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-associated-entity.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-associated-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-24T14:52:25+00:00</t>
+    <t>2025-04-28T07:47:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-associated-entity.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-associated-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T07:47:42+00:00</t>
+    <t>2025-04-28T07:48:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-associated-entity.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-associated-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T07:48:19+00:00</t>
+    <t>2025-04-28T09:06:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-associated-entity.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-associated-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T09:06:14+00:00</t>
+    <t>2025-04-28T09:53:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-associated-entity.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-associated-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T09:53:39+00:00</t>
+    <t>2025-05-06T15:44:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-associated-entity.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-associated-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-06T15:44:46+00:00</t>
+    <t>2025-05-06T15:53:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-associated-entity.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-associated-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-06T15:53:54+00:00</t>
+    <t>2025-05-06T15:58:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-associated-entity.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-associated-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-06T15:58:22+00:00</t>
+    <t>2025-05-20T10:20:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-associated-entity.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-associated-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T10:20:09+00:00</t>
+    <t>2025-05-20T12:44:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
